--- a/OUTPUT/reverse_A1B3Z0.xlsx
+++ b/OUTPUT/reverse_A1B3Z0.xlsx
@@ -425,14 +425,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>coords</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>group1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>group2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>p_value</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[(10, 7), (11, 6)]</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.999999982869012</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3318</v>
       </c>
     </row>
   </sheetData>
